--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148468</v>
       </c>
       <c r="B2" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129148630</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129148440</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129148536</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148468</v>
       </c>
       <c r="B2" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129148630</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129148440</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129148536</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148468</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129148630</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129148440</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>129148711</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129148536</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148468</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129148630</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129148440</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129148536</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148468</v>
       </c>
       <c r="B2" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129148630</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129148440</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>129148711</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129148536</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148468</v>
       </c>
       <c r="B2" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129148630</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129148440</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129148536</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148468</v>
       </c>
       <c r="B2" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129148630</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129148440</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129148536</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148468</v>
       </c>
       <c r="B2" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129148630</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129148440</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129148536</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148468</v>
       </c>
       <c r="B2" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129148630</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129148440</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129148536</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148468</v>
       </c>
       <c r="B2" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129148630</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129148440</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129148536</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148468</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129148630</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129148440</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129148536</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148468</v>
       </c>
       <c r="B2" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129148630</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129148440</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129148536</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148468</v>
       </c>
       <c r="B2" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129148630</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129148440</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129148536</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1200,6 +1200,127 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129603483</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>469315</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6859640</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,6 +1321,310 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129647999</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80150</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Frägnvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>469318</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6859679</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129648000</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Frägnvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>469318</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6859679</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129648003</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Frägnvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>469313</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6859656</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1625,6 +1625,104 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129657341</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Frägnvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>469329</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6859642</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129148468</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129148630</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129148440</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>129148711</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129148536</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>129603483</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>129647999</v>
       </c>
       <c r="B8" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129648000</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>129648003</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>129657341</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -1205,7 +1205,7 @@
         <v>129603483</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>129647999</v>
       </c>
       <c r="B8" t="n">
-        <v>80176</v>
+        <v>80181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129648000</v>
       </c>
       <c r="B9" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>129648003</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>129657341</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -1205,7 +1205,7 @@
         <v>129603483</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>129647999</v>
       </c>
       <c r="B8" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129648000</v>
       </c>
       <c r="B9" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>129648003</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>129657341</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -1205,7 +1205,7 @@
         <v>129603483</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>129647999</v>
       </c>
       <c r="B8" t="n">
-        <v>80182</v>
+        <v>80187</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129648000</v>
       </c>
       <c r="B9" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>129648003</v>
       </c>
       <c r="B10" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>129657341</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -1205,7 +1205,7 @@
         <v>129603483</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>129648003</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -1205,7 +1205,7 @@
         <v>129603483</v>
       </c>
       <c r="B7" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>129648003</v>
       </c>
       <c r="B10" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -1205,7 +1205,7 @@
         <v>129603483</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>129648003</v>
       </c>
       <c r="B10" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -1205,7 +1205,7 @@
         <v>129603483</v>
       </c>
       <c r="B7" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>129647999</v>
       </c>
       <c r="B8" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129648000</v>
       </c>
       <c r="B9" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>129648003</v>
       </c>
       <c r="B10" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>129657341</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -1205,7 +1205,7 @@
         <v>129603483</v>
       </c>
       <c r="B7" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>129647999</v>
       </c>
       <c r="B8" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129648000</v>
       </c>
       <c r="B9" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>129648003</v>
       </c>
       <c r="B10" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>129657341</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -1326,7 +1326,7 @@
         <v>129647999</v>
       </c>
       <c r="B8" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129648000</v>
       </c>
       <c r="B9" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>129648003</v>
       </c>
       <c r="B10" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>129657341</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1723,6 +1723,104 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129658160</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Frägnvallen 4, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>469169</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6859626</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -1728,7 +1728,7 @@
         <v>129658160</v>
       </c>
       <c r="B12" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -1728,7 +1728,7 @@
         <v>129658160</v>
       </c>
       <c r="B12" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31853-2025 artfynd.xlsx
+++ b/artfynd/A 31853-2025 artfynd.xlsx
@@ -1728,7 +1728,7 @@
         <v>129658160</v>
       </c>
       <c r="B12" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
